--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.57083578185623</v>
+        <v>4.805260814551637</v>
       </c>
       <c r="D2" t="n">
-        <v>30.75068851628487</v>
+        <v>4.996986883896292</v>
       </c>
       <c r="E2" t="n">
-        <v>7.681693755578872</v>
+        <v>1.248275235281567</v>
       </c>
       <c r="F2" t="n">
-        <v>3.573523516861927</v>
+        <v>0.5806975714900631</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.20744827069849</v>
+        <v>2.308710343988504</v>
       </c>
       <c r="D3" t="n">
-        <v>37.89773555000873</v>
+        <v>6.158382026876418</v>
       </c>
       <c r="E3" t="n">
-        <v>7.681693755578872</v>
+        <v>1.248275235281567</v>
       </c>
       <c r="F3" t="n">
-        <v>3.573523516861927</v>
+        <v>0.5806975714900631</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
